--- a/data/macro/USA/US Consumer Sentiment.xlsx
+++ b/data/macro/USA/US Consumer Sentiment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA85EC5-DC64-4D1A-99AB-82EEAB2897BC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82873BD5-7D2D-4768-9E67-A266FA8290F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" xr2:uid="{586DF7D0-555B-4D57-B9C4-61D266B9D418}"/>
   </bookViews>
@@ -80,7 +80,7 @@
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="178" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="181" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="180" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -197,10 +197,10 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1">
@@ -522,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90BA518E-4188-4051-9904-37DCC06068B4}">
-  <dimension ref="A1:H823"/>
+  <dimension ref="A1:H824"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="10" bestFit="1" customWidth="1"/>
@@ -15856,7 +15856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="753" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B753" s="7">
         <v>45016</v>
       </c>
@@ -15877,7 +15877,7 @@
         <v>63.4</v>
       </c>
     </row>
-    <row r="754" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B754" s="7">
         <v>45030</v>
       </c>
@@ -15901,7 +15901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="755" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B755" s="7">
         <v>45044</v>
       </c>
@@ -15922,7 +15922,7 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="756" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B756" s="7">
         <v>45058</v>
       </c>
@@ -15946,7 +15946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="757" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B757" s="7">
         <v>45072</v>
       </c>
@@ -15967,7 +15967,7 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="758" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B758" s="7">
         <v>45093</v>
       </c>
@@ -15991,7 +15991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="759" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B759" s="7">
         <v>45107</v>
       </c>
@@ -16012,7 +16012,7 @@
         <v>59.2</v>
       </c>
     </row>
-    <row r="760" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B760" s="7">
         <v>45121</v>
       </c>
@@ -16036,7 +16036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="761" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B761" s="7">
         <v>45135</v>
       </c>
@@ -16057,7 +16057,7 @@
         <v>64.400000000000006</v>
       </c>
     </row>
-    <row r="762" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B762" s="7">
         <v>45149</v>
       </c>
@@ -16081,7 +16081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="763" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B763" s="7">
         <v>45163</v>
       </c>
@@ -16102,7 +16102,7 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="764" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B764" s="7">
         <v>45184</v>
       </c>
@@ -16126,7 +16126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="765" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B765" s="7">
         <v>45198</v>
       </c>
@@ -16147,7 +16147,10 @@
         <v>69.5</v>
       </c>
     </row>
-    <row r="766" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A766" s="11">
+        <v>45200</v>
+      </c>
       <c r="B766" s="7">
         <v>45212</v>
       </c>
@@ -16171,7 +16174,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="767" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A767" s="11">
+        <v>45200</v>
+      </c>
       <c r="B767" s="7">
         <v>45226</v>
       </c>
@@ -16192,7 +16198,10 @@
         <v>68.099999999999994</v>
       </c>
     </row>
-    <row r="768" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A768" s="11">
+        <v>45231</v>
+      </c>
       <c r="B768" s="7">
         <v>45240</v>
       </c>
@@ -16216,7 +16225,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="769" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A769" s="11">
+        <v>45231</v>
+      </c>
       <c r="B769" s="7">
         <v>45252</v>
       </c>
@@ -16237,7 +16249,10 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="770" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A770" s="11">
+        <v>45261</v>
+      </c>
       <c r="B770" s="7">
         <v>45268</v>
       </c>
@@ -16261,7 +16276,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="771" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A771" s="11">
+        <v>45261</v>
+      </c>
       <c r="B771" s="7">
         <v>45282</v>
       </c>
@@ -16269,7 +16287,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D771" s="8" t="str">
-        <f t="shared" ref="D771:D823" si="12">IF(
+        <f t="shared" ref="D771:D824" si="12">IF(
  AND(
   B771 &gt;= IF(
          YEAR(B771)&gt;=2007,
@@ -16297,7 +16315,10 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="772" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A772" s="11">
+        <v>45292</v>
+      </c>
       <c r="B772" s="7">
         <v>45310</v>
       </c>
@@ -16321,7 +16342,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="773" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A773" s="11">
+        <v>45292</v>
+      </c>
       <c r="B773" s="7">
         <v>45324</v>
       </c>
@@ -16342,7 +16366,10 @@
         <v>69.7</v>
       </c>
     </row>
-    <row r="774" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A774" s="11">
+        <v>45323</v>
+      </c>
       <c r="B774" s="7">
         <v>45338</v>
       </c>
@@ -16366,7 +16393,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="775" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A775" s="11">
+        <v>45323</v>
+      </c>
       <c r="B775" s="7">
         <v>45352</v>
       </c>
@@ -16387,7 +16417,10 @@
         <v>79</v>
       </c>
     </row>
-    <row r="776" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A776" s="11">
+        <v>45352</v>
+      </c>
       <c r="B776" s="7">
         <v>45366</v>
       </c>
@@ -16411,7 +16444,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="777" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A777" s="11">
+        <v>45352</v>
+      </c>
       <c r="B777" s="7">
         <v>45379</v>
       </c>
@@ -16432,7 +16468,10 @@
         <v>76.900000000000006</v>
       </c>
     </row>
-    <row r="778" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A778" s="11">
+        <v>45383</v>
+      </c>
       <c r="B778" s="7">
         <v>45394</v>
       </c>
@@ -16456,7 +16495,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="779" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A779" s="11">
+        <v>45383</v>
+      </c>
       <c r="B779" s="7">
         <v>45408</v>
       </c>
@@ -16477,7 +16519,10 @@
         <v>79.400000000000006</v>
       </c>
     </row>
-    <row r="780" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A780" s="11">
+        <v>45413</v>
+      </c>
       <c r="B780" s="7">
         <v>45422</v>
       </c>
@@ -16501,7 +16546,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="781" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A781" s="11">
+        <v>45413</v>
+      </c>
       <c r="B781" s="7">
         <v>45436</v>
       </c>
@@ -16522,7 +16570,10 @@
         <v>77.2</v>
       </c>
     </row>
-    <row r="782" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A782" s="11">
+        <v>45444</v>
+      </c>
       <c r="B782" s="7">
         <v>45457</v>
       </c>
@@ -16546,7 +16597,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="783" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A783" s="11">
+        <v>45444</v>
+      </c>
       <c r="B783" s="7">
         <v>45471</v>
       </c>
@@ -16567,7 +16621,10 @@
         <v>69.099999999999994</v>
       </c>
     </row>
-    <row r="784" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A784" s="11">
+        <v>45474</v>
+      </c>
       <c r="B784" s="7">
         <v>45485</v>
       </c>
@@ -16592,6 +16649,9 @@
       </c>
     </row>
     <row r="785" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A785" s="11">
+        <v>45474</v>
+      </c>
       <c r="B785" s="7">
         <v>45499</v>
       </c>
@@ -16613,6 +16673,9 @@
       </c>
     </row>
     <row r="786" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A786" s="11">
+        <v>45505</v>
+      </c>
       <c r="B786" s="7">
         <v>45520</v>
       </c>
@@ -16637,6 +16700,9 @@
       </c>
     </row>
     <row r="787" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A787" s="11">
+        <v>45505</v>
+      </c>
       <c r="B787" s="7">
         <v>45534</v>
       </c>
@@ -16658,6 +16724,9 @@
       </c>
     </row>
     <row r="788" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A788" s="11">
+        <v>45536</v>
+      </c>
       <c r="B788" s="7">
         <v>45548</v>
       </c>
@@ -16682,6 +16751,9 @@
       </c>
     </row>
     <row r="789" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A789" s="11">
+        <v>45536</v>
+      </c>
       <c r="B789" s="7">
         <v>45562</v>
       </c>
@@ -16703,6 +16775,9 @@
       </c>
     </row>
     <row r="790" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A790" s="11">
+        <v>45566</v>
+      </c>
       <c r="B790" s="7">
         <v>45576</v>
       </c>
@@ -16727,6 +16802,9 @@
       </c>
     </row>
     <row r="791" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A791" s="11">
+        <v>45566</v>
+      </c>
       <c r="B791" s="7">
         <v>45590</v>
       </c>
@@ -16748,6 +16826,9 @@
       </c>
     </row>
     <row r="792" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A792" s="11">
+        <v>45597</v>
+      </c>
       <c r="B792" s="7">
         <v>45604</v>
       </c>
@@ -16772,6 +16853,9 @@
       </c>
     </row>
     <row r="793" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A793" s="11">
+        <v>45597</v>
+      </c>
       <c r="B793" s="7">
         <v>45618</v>
       </c>
@@ -16793,6 +16877,9 @@
       </c>
     </row>
     <row r="794" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A794" s="11">
+        <v>45627</v>
+      </c>
       <c r="B794" s="7">
         <v>45632</v>
       </c>
@@ -16817,6 +16904,9 @@
       </c>
     </row>
     <row r="795" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A795" s="11">
+        <v>45627</v>
+      </c>
       <c r="B795" s="7">
         <v>45646</v>
       </c>
@@ -17538,11 +17628,35 @@
         <f t="shared" si="12"/>
         <v>UTC-5</v>
       </c>
+      <c r="E823" s="9">
+        <v>56.6</v>
+      </c>
       <c r="F823" s="9">
         <v>57.3</v>
       </c>
       <c r="G823" s="9">
         <v>56.4</v>
+      </c>
+    </row>
+    <row r="824" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A824" s="11">
+        <v>46082</v>
+      </c>
+      <c r="B824" s="7">
+        <v>46094</v>
+      </c>
+      <c r="C824" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D824" s="8" t="str">
+        <f t="shared" si="12"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="G824" s="9">
+        <v>56.6</v>
+      </c>
+      <c r="H824" s="6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/macro/USA/US Consumer Sentiment.xlsx
+++ b/data/macro/USA/US Consumer Sentiment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5682408-69F4-4EBE-82B3-A7FA464C73BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09346A7-4898-4812-A1BE-45C87926BAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{586DF7D0-555B-4D57-B9C4-61D266B9D418}"/>
   </bookViews>
@@ -5240,6 +5240,9 @@
                 </c:pt>
                 <c:pt idx="824">
                   <c:v>47.6</c:v>
+                </c:pt>
+                <c:pt idx="825">
+                  <c:v>49.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -23557,6 +23560,15 @@
         <f t="shared" si="12"/>
         <v>UTC-4</v>
       </c>
+      <c r="E827" s="9">
+        <v>49.8</v>
+      </c>
+      <c r="F827" s="9">
+        <v>47.3</v>
+      </c>
+      <c r="G827" s="9">
+        <v>53.3</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
